--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/25.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/25.xlsx
@@ -426,13 +426,13 @@
         <v>-14.14249798036931</v>
       </c>
       <c r="E2">
-        <v>-7.320633531079333</v>
+        <v>-9.432084350369722</v>
       </c>
       <c r="F2">
-        <v>0.10886963442164</v>
+        <v>-1.18198609351728</v>
       </c>
       <c r="G2">
-        <v>-12.18018347257366</v>
+        <v>-12.3880360742568</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.69006952971369</v>
       </c>
       <c r="E3">
-        <v>-7.910557840058551</v>
+        <v>-8.999479228416972</v>
       </c>
       <c r="F3">
-        <v>0.2912420809670273</v>
+        <v>-1.312888097810885</v>
       </c>
       <c r="G3">
-        <v>-12.38838368153842</v>
+        <v>-11.05397560666007</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.19942617773329</v>
       </c>
       <c r="E4">
-        <v>-8.293648627211432</v>
+        <v>-9.758958661191384</v>
       </c>
       <c r="F4">
-        <v>0.0100107519151211</v>
+        <v>-0.8412216753980892</v>
       </c>
       <c r="G4">
-        <v>-11.36817286270122</v>
+        <v>-11.46072909488817</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.69527306018483</v>
       </c>
       <c r="E5">
-        <v>-9.377326042668972</v>
+        <v>-11.75284123829463</v>
       </c>
       <c r="F5">
-        <v>0.3727071214042748</v>
+        <v>-0.9401557839355915</v>
       </c>
       <c r="G5">
-        <v>-11.1600521068294</v>
+        <v>-11.43729043247013</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.15396394780947</v>
       </c>
       <c r="E6">
-        <v>-10.16559751318415</v>
+        <v>-10.59947060785905</v>
       </c>
       <c r="F6">
-        <v>0.8910516919687327</v>
+        <v>-0.6621480882745623</v>
       </c>
       <c r="G6">
-        <v>-10.81768210824905</v>
+        <v>-10.74629681478575</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.58839976408894</v>
       </c>
       <c r="E7">
-        <v>-11.19842469400956</v>
+        <v>-12.0454168869822</v>
       </c>
       <c r="F7">
-        <v>0.9339162762760168</v>
+        <v>-0.6712393520821425</v>
       </c>
       <c r="G7">
-        <v>-11.13582222402747</v>
+        <v>-10.12497031742979</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.99616574789752</v>
       </c>
       <c r="E8">
-        <v>-11.25954097921708</v>
+        <v>-13.40775395050174</v>
       </c>
       <c r="F8">
-        <v>0.7002008758050403</v>
+        <v>-0.9506145778011537</v>
       </c>
       <c r="G8">
-        <v>-10.45189993161498</v>
+        <v>-10.25097299119999</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.40869906871516</v>
       </c>
       <c r="E9">
-        <v>-13.02398842072171</v>
+        <v>-14.22242642448163</v>
       </c>
       <c r="F9">
-        <v>1.250621034127851</v>
+        <v>-0.5955873042075155</v>
       </c>
       <c r="G9">
-        <v>-9.669310139950046</v>
+        <v>-9.429878244367798</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.841862539247712</v>
       </c>
       <c r="E10">
-        <v>-13.75813556989721</v>
+        <v>-15.32189462880392</v>
       </c>
       <c r="F10">
-        <v>1.256224185656676</v>
+        <v>-0.2292587052013015</v>
       </c>
       <c r="G10">
-        <v>-8.805264375291346</v>
+        <v>-7.715462578673123</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.316378653509487</v>
       </c>
       <c r="E11">
-        <v>-14.97524447199076</v>
+        <v>-16.47919144620415</v>
       </c>
       <c r="F11">
-        <v>1.08921764575584</v>
+        <v>-0.5554498614866181</v>
       </c>
       <c r="G11">
-        <v>-8.005516026096368</v>
+        <v>-7.738772129815132</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.850251102014964</v>
       </c>
       <c r="E12">
-        <v>-15.51310491530379</v>
+        <v>-16.75922322189048</v>
       </c>
       <c r="F12">
-        <v>1.431326630197238</v>
+        <v>-0.09940748978259033</v>
       </c>
       <c r="G12">
-        <v>-7.642200205889052</v>
+        <v>-8.103862402431497</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.439048725453199</v>
       </c>
       <c r="E13">
-        <v>-14.926382237448</v>
+        <v>-16.83482156697452</v>
       </c>
       <c r="F13">
-        <v>1.447944456367945</v>
+        <v>0.1916697389456029</v>
       </c>
       <c r="G13">
-        <v>-6.822661415460312</v>
+        <v>-7.755463900424138</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.087940436300972</v>
       </c>
       <c r="E14">
-        <v>-17.19358086328419</v>
+        <v>-18.83977626302653</v>
       </c>
       <c r="F14">
-        <v>1.630642354478955</v>
+        <v>0.7517758426472414</v>
       </c>
       <c r="G14">
-        <v>-6.658167028705006</v>
+        <v>-7.207283906758379</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.778801292091721</v>
       </c>
       <c r="E15">
-        <v>-18.0350030332274</v>
+        <v>-18.92935400737226</v>
       </c>
       <c r="F15">
-        <v>1.527950111804115</v>
+        <v>0.2424203868588177</v>
       </c>
       <c r="G15">
-        <v>-5.496814411346516</v>
+        <v>-6.240117959096919</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.495151797941599</v>
       </c>
       <c r="E16">
-        <v>-18.42567901434313</v>
+        <v>-19.21637774692642</v>
       </c>
       <c r="F16">
-        <v>1.86393807288234</v>
+        <v>0.4026621269418542</v>
       </c>
       <c r="G16">
-        <v>-5.14644282419775</v>
+        <v>-6.148184109471358</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.222320580527031</v>
       </c>
       <c r="E17">
-        <v>-19.99729950412715</v>
+        <v>-20.42933403835493</v>
       </c>
       <c r="F17">
-        <v>1.856608681905686</v>
+        <v>0.9511960915193767</v>
       </c>
       <c r="G17">
-        <v>-4.831374894679772</v>
+        <v>-5.84846717961898</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.935880469378568</v>
       </c>
       <c r="E18">
-        <v>-20.86320713302983</v>
+        <v>-21.88769286473311</v>
       </c>
       <c r="F18">
-        <v>1.599733166127323</v>
+        <v>1.38116749644344</v>
       </c>
       <c r="G18">
-        <v>-4.666420342094507</v>
+        <v>-4.890415163827135</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.626393118463856</v>
       </c>
       <c r="E19">
-        <v>-21.88215001254772</v>
+        <v>-22.3126448656129</v>
       </c>
       <c r="F19">
-        <v>2.023239883504563</v>
+        <v>1.327717421797359</v>
       </c>
       <c r="G19">
-        <v>-4.496026563188219</v>
+        <v>-5.413348937210412</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.277936541458753</v>
       </c>
       <c r="E20">
-        <v>-21.99659813614357</v>
+        <v>-23.3383261144542</v>
       </c>
       <c r="F20">
-        <v>2.540486154016663</v>
+        <v>1.482342548851289</v>
       </c>
       <c r="G20">
-        <v>-3.59876278458847</v>
+        <v>-4.878937502442481</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.88666742309692</v>
       </c>
       <c r="E21">
-        <v>-22.90924414527942</v>
+        <v>-22.59785721556399</v>
       </c>
       <c r="F21">
-        <v>2.178351208274533</v>
+        <v>1.766137897780292</v>
       </c>
       <c r="G21">
-        <v>-3.791175001876451</v>
+        <v>-5.247053613681741</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.457734429263501</v>
       </c>
       <c r="E22">
-        <v>-23.85592616505691</v>
+        <v>-24.28779314574641</v>
       </c>
       <c r="F22">
-        <v>2.714799913011337</v>
+        <v>2.278628299428328</v>
       </c>
       <c r="G22">
-        <v>-3.472538304267139</v>
+        <v>-3.871296825017892</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.999035903936829</v>
       </c>
       <c r="E23">
-        <v>-23.79292603466221</v>
+        <v>-24.89195044853174</v>
       </c>
       <c r="F23">
-        <v>2.76935383068048</v>
+        <v>1.89732734469755</v>
       </c>
       <c r="G23">
-        <v>-2.53112509035567</v>
+        <v>-5.263665931197804</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.536231018362758</v>
       </c>
       <c r="E24">
-        <v>-23.56167950946052</v>
+        <v>-25.31433933312318</v>
       </c>
       <c r="F24">
-        <v>2.701541127087278</v>
+        <v>2.122267430691076</v>
       </c>
       <c r="G24">
-        <v>-2.279368033730714</v>
+        <v>-5.232924205320131</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.088671224442583</v>
       </c>
       <c r="E25">
-        <v>-24.30019663605342</v>
+        <v>-25.22640089636823</v>
       </c>
       <c r="F25">
-        <v>2.716196741628755</v>
+        <v>2.19661133747955</v>
       </c>
       <c r="G25">
-        <v>-3.388751707213724</v>
+        <v>-4.4515063467761</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.683043865804406</v>
       </c>
       <c r="E26">
-        <v>-24.87225158659837</v>
+        <v>-25.59385486277263</v>
       </c>
       <c r="F26">
-        <v>2.802914142734557</v>
+        <v>2.63069562666601</v>
       </c>
       <c r="G26">
-        <v>-2.30713688971412</v>
+        <v>-4.486743793496102</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.339918300070768</v>
       </c>
       <c r="E27">
-        <v>-24.98079458008822</v>
+        <v>-25.7231926089057</v>
       </c>
       <c r="F27">
-        <v>2.932065360138644</v>
+        <v>2.192599810395742</v>
       </c>
       <c r="G27">
-        <v>-2.91377449651233</v>
+        <v>-4.557566294217731</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.07112264886476</v>
       </c>
       <c r="E28">
-        <v>-24.61147941086668</v>
+        <v>-25.58461224732297</v>
       </c>
       <c r="F28">
-        <v>2.929452245378169</v>
+        <v>2.238204205936736</v>
       </c>
       <c r="G28">
-        <v>-2.636049520677331</v>
+        <v>-5.579233753092212</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.888048085440407</v>
       </c>
       <c r="E29">
-        <v>-24.59237377902831</v>
+        <v>-26.0496774709627</v>
       </c>
       <c r="F29">
-        <v>2.940791579732716</v>
+        <v>2.400540397092942</v>
       </c>
       <c r="G29">
-        <v>-3.065956964407087</v>
+        <v>-4.91523763428059</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.784670732166587</v>
       </c>
       <c r="E30">
-        <v>-24.58022841173974</v>
+        <v>-25.28384458915553</v>
       </c>
       <c r="F30">
-        <v>2.949568477916081</v>
+        <v>2.33604397368667</v>
       </c>
       <c r="G30">
-        <v>-2.6887004369339</v>
+        <v>-4.864076463516693</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.756086245868956</v>
       </c>
       <c r="E31">
-        <v>-24.39629538297019</v>
+        <v>-24.65638828760074</v>
       </c>
       <c r="F31">
-        <v>2.883545362007326</v>
+        <v>2.452611063886675</v>
       </c>
       <c r="G31">
-        <v>-2.872932296194341</v>
+        <v>-4.078914377967745</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.787463210041126</v>
       </c>
       <c r="E32">
-        <v>-23.77943571059335</v>
+        <v>-23.62909943048671</v>
       </c>
       <c r="F32">
-        <v>2.918163589612917</v>
+        <v>2.409572271928692</v>
       </c>
       <c r="G32">
-        <v>-3.461289070524695</v>
+        <v>-5.828703222749532</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.86285266570594</v>
       </c>
       <c r="E33">
-        <v>-23.65142933581854</v>
+        <v>-23.40025299650909</v>
       </c>
       <c r="F33">
-        <v>2.920385529012278</v>
+        <v>2.378832540110013</v>
       </c>
       <c r="G33">
-        <v>-4.20381132952783</v>
+        <v>-4.795942125772953</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.971777097402581</v>
       </c>
       <c r="E34">
-        <v>-23.92325551660296</v>
+        <v>-24.66960237475513</v>
       </c>
       <c r="F34">
-        <v>3.057749845293834</v>
+        <v>2.115897765499179</v>
       </c>
       <c r="G34">
-        <v>-3.728615622820843</v>
+        <v>-5.112466695328211</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.100259631851174</v>
       </c>
       <c r="E35">
-        <v>-22.33803149089989</v>
+        <v>-23.36402067597372</v>
       </c>
       <c r="F35">
-        <v>3.115705563269341</v>
+        <v>1.878745723191698</v>
       </c>
       <c r="G35">
-        <v>-3.941083124985729</v>
+        <v>-4.964058249348223</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.244949067708827</v>
       </c>
       <c r="E36">
-        <v>-22.76234044847059</v>
+        <v>-23.43692910749721</v>
       </c>
       <c r="F36">
-        <v>3.145818147545506</v>
+        <v>1.946119740246324</v>
       </c>
       <c r="G36">
-        <v>-4.083641836997825</v>
+        <v>-4.828885364434241</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.397662721409296</v>
       </c>
       <c r="E37">
-        <v>-21.40461337149086</v>
+        <v>-21.61016986364704</v>
       </c>
       <c r="F37">
-        <v>2.798264382166827</v>
+        <v>2.491614573172118</v>
       </c>
       <c r="G37">
-        <v>-3.937342208526353</v>
+        <v>-4.624008943190904</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.553594184408616</v>
       </c>
       <c r="E38">
-        <v>-21.20642470654517</v>
+        <v>-22.73534621491087</v>
       </c>
       <c r="F38">
-        <v>2.963074321962949</v>
+        <v>1.843220032096561</v>
       </c>
       <c r="G38">
-        <v>-4.182219951520703</v>
+        <v>-5.316157941268488</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.709284538986238</v>
       </c>
       <c r="E39">
-        <v>-20.49116129398165</v>
+        <v>-23.1151583868822</v>
       </c>
       <c r="F39">
-        <v>2.792637475049271</v>
+        <v>1.85831908429436</v>
       </c>
       <c r="G39">
-        <v>-4.246338597525307</v>
+        <v>-5.573112554390099</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.858544234680778</v>
       </c>
       <c r="E40">
-        <v>-20.35860833130313</v>
+        <v>-21.00224939896134</v>
       </c>
       <c r="F40">
-        <v>2.886850556252848</v>
+        <v>2.516716311931833</v>
       </c>
       <c r="G40">
-        <v>-4.197551087913068</v>
+        <v>-4.296804553725957</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.004982636372145</v>
       </c>
       <c r="E41">
-        <v>-19.46210180353063</v>
+        <v>-20.66696571190743</v>
       </c>
       <c r="F41">
-        <v>2.973784925069066</v>
+        <v>1.894441832519619</v>
       </c>
       <c r="G41">
-        <v>-4.161439657170698</v>
+        <v>-5.656084757240853</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.148493138191224</v>
       </c>
       <c r="E42">
-        <v>-18.99886608338999</v>
+        <v>-20.06011396708755</v>
       </c>
       <c r="F42">
-        <v>2.794162583845839</v>
+        <v>1.946376300604625</v>
       </c>
       <c r="G42">
-        <v>-4.083919922823124</v>
+        <v>-5.363995324310957</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.295976337033794</v>
       </c>
       <c r="E43">
-        <v>-17.89841520020805</v>
+        <v>-20.18474210025264</v>
       </c>
       <c r="F43">
-        <v>3.078369696312856</v>
+        <v>2.137073497294519</v>
       </c>
       <c r="G43">
-        <v>-3.775886902576097</v>
+        <v>-5.43824755021127</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.45280704813098</v>
       </c>
       <c r="E44">
-        <v>-17.46468701670139</v>
+        <v>-19.05156846389126</v>
       </c>
       <c r="F44">
-        <v>3.026053555102229</v>
+        <v>1.455259593991359</v>
       </c>
       <c r="G44">
-        <v>-3.5252223259791</v>
+        <v>-5.90447829959791</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.619901069404547</v>
       </c>
       <c r="E45">
-        <v>-17.94021754377285</v>
+        <v>-18.85070347080704</v>
       </c>
       <c r="F45">
-        <v>3.005078953958149</v>
+        <v>1.679841762447997</v>
       </c>
       <c r="G45">
-        <v>-4.128370617778918</v>
+        <v>-4.189182028789791</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.804634317602691</v>
       </c>
       <c r="E46">
-        <v>-16.81062593035154</v>
+        <v>-17.56797698034235</v>
       </c>
       <c r="F46">
-        <v>2.967286979698017</v>
+        <v>2.188646880430805</v>
       </c>
       <c r="G46">
-        <v>-3.945946316382918</v>
+        <v>-4.746949362337278</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.00374748703741</v>
       </c>
       <c r="E47">
-        <v>-15.46165692210265</v>
+        <v>-17.07310081231012</v>
       </c>
       <c r="F47">
-        <v>3.049528827886788</v>
+        <v>1.41001469969317</v>
       </c>
       <c r="G47">
-        <v>-4.498817353077825</v>
+        <v>-5.199934619021295</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.220988078159016</v>
       </c>
       <c r="E48">
-        <v>-15.21044435500114</v>
+        <v>-17.49929814354202</v>
       </c>
       <c r="F48">
-        <v>2.797602393094173</v>
+        <v>1.86567064715383</v>
       </c>
       <c r="G48">
-        <v>-3.677487557512339</v>
+        <v>-4.921305864254074</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.456447620633491</v>
       </c>
       <c r="E49">
-        <v>-14.21782549488984</v>
+        <v>-16.05943360501117</v>
       </c>
       <c r="F49">
-        <v>3.070256370908059</v>
+        <v>1.853137198539043</v>
       </c>
       <c r="G49">
-        <v>-3.924606539836776</v>
+        <v>-5.726314670310952</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.70825020166242</v>
       </c>
       <c r="E50">
-        <v>-14.3415479332534</v>
+        <v>-15.15241648906686</v>
       </c>
       <c r="F50">
-        <v>3.221859787075331</v>
+        <v>1.623995540751855</v>
       </c>
       <c r="G50">
-        <v>-4.030226184721684</v>
+        <v>-5.424780250957514</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.982977196144944</v>
       </c>
       <c r="E51">
-        <v>-13.76186703247953</v>
+        <v>-14.96095260802255</v>
       </c>
       <c r="F51">
-        <v>2.934773497254045</v>
+        <v>1.391303214302253</v>
       </c>
       <c r="G51">
-        <v>-4.015467772707614</v>
+        <v>-5.295728564745645</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.275640443328155</v>
       </c>
       <c r="E52">
-        <v>-13.13684704994087</v>
+        <v>-15.05681134581692</v>
       </c>
       <c r="F52">
-        <v>2.633522541725069</v>
+        <v>1.541986497332654</v>
       </c>
       <c r="G52">
-        <v>-4.355123123945758</v>
+        <v>-6.13872588086566</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.591987081801595</v>
       </c>
       <c r="E53">
-        <v>-12.48542153546348</v>
+        <v>-14.57384053595086</v>
       </c>
       <c r="F53">
-        <v>3.189313046807135</v>
+        <v>1.320066538519871</v>
       </c>
       <c r="G53">
-        <v>-4.28762110040002</v>
+        <v>-5.269413038253979</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.929811973387425</v>
       </c>
       <c r="E54">
-        <v>-11.74375711943525</v>
+        <v>-13.51335796436061</v>
       </c>
       <c r="F54">
-        <v>2.98906293603531</v>
+        <v>1.421721453820098</v>
       </c>
       <c r="G54">
-        <v>-5.046457727820682</v>
+        <v>-6.529115342493137</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.285358489950944</v>
       </c>
       <c r="E55">
-        <v>-10.84369121109271</v>
+        <v>-13.55272851738329</v>
       </c>
       <c r="F55">
-        <v>2.623074833800915</v>
+        <v>1.272666220470768</v>
       </c>
       <c r="G55">
-        <v>-4.395856076260952</v>
+        <v>-5.50193251475023</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.660240102787121</v>
       </c>
       <c r="E56">
-        <v>-11.39115654777601</v>
+        <v>-13.33943286314801</v>
       </c>
       <c r="F56">
-        <v>2.882672740047919</v>
+        <v>1.610751008181035</v>
       </c>
       <c r="G56">
-        <v>-4.907447920626685</v>
+        <v>-5.920640382920632</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.04139689757613</v>
       </c>
       <c r="E57">
-        <v>-9.860156469840792</v>
+        <v>-12.0813684421291</v>
       </c>
       <c r="F57">
-        <v>3.164668999056982</v>
+        <v>1.619776548193125</v>
       </c>
       <c r="G57">
-        <v>-5.207413141394508</v>
+        <v>-6.117631084689425</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.429198449660534</v>
       </c>
       <c r="E58">
-        <v>-10.3481719997514</v>
+        <v>-11.19830242521135</v>
       </c>
       <c r="F58">
-        <v>2.862795647103238</v>
+        <v>1.395764513866046</v>
       </c>
       <c r="G58">
-        <v>-5.543430203084994</v>
+        <v>-6.72215325288804</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.813006703121063</v>
       </c>
       <c r="E59">
-        <v>-10.09605373784836</v>
+        <v>-10.56226919388603</v>
       </c>
       <c r="F59">
-        <v>3.143600959263891</v>
+        <v>1.417252235726728</v>
       </c>
       <c r="G59">
-        <v>-5.593240671268869</v>
+        <v>-6.155222329287849</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.185118603251906</v>
       </c>
       <c r="E60">
-        <v>-8.956630807356396</v>
+        <v>-11.75678101068131</v>
       </c>
       <c r="F60">
-        <v>2.805685628086576</v>
+        <v>1.42271760484091</v>
       </c>
       <c r="G60">
-        <v>-5.982776012147212</v>
+        <v>-6.55421920931743</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.545295511839228</v>
       </c>
       <c r="E61">
-        <v>-9.565330169571414</v>
+        <v>-11.18765145434531</v>
       </c>
       <c r="F61">
-        <v>2.754756813257874</v>
+        <v>1.013871253122893</v>
       </c>
       <c r="G61">
-        <v>-6.154927690734854</v>
+        <v>-6.363270253157808</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.881632992194888</v>
       </c>
       <c r="E62">
-        <v>-8.932543854109596</v>
+        <v>-11.51548127318259</v>
       </c>
       <c r="F62">
-        <v>2.813767279373064</v>
+        <v>1.176850428880766</v>
       </c>
       <c r="G62">
-        <v>-5.856991834382604</v>
+        <v>-6.631679353845297</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.20048379802523</v>
       </c>
       <c r="E63">
-        <v>-8.908615397453067</v>
+        <v>-10.85080544375876</v>
       </c>
       <c r="F63">
-        <v>2.792639058755186</v>
+        <v>1.178697029978169</v>
       </c>
       <c r="G63">
-        <v>-6.059583979203843</v>
+        <v>-6.770553428672184</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.49595691722062</v>
       </c>
       <c r="E64">
-        <v>-7.841815604622115</v>
+        <v>-9.551423225893858</v>
       </c>
       <c r="F64">
-        <v>2.419424506428641</v>
+        <v>0.9426013195162868</v>
       </c>
       <c r="G64">
-        <v>-5.648917426148331</v>
+        <v>-6.774108954581362</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.76626856811452</v>
       </c>
       <c r="E65">
-        <v>-7.63256840614969</v>
+        <v>-10.08955537764735</v>
       </c>
       <c r="F65">
-        <v>2.770817174946346</v>
+        <v>0.9998285327706912</v>
       </c>
       <c r="G65">
-        <v>-6.675779130973929</v>
+        <v>-6.266754608505895</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.01385983261589</v>
       </c>
       <c r="E66">
-        <v>-7.814531548725901</v>
+        <v>-9.533848218270089</v>
       </c>
       <c r="F66">
-        <v>2.392773903283626</v>
+        <v>0.8783281986440922</v>
       </c>
       <c r="G66">
-        <v>-6.241985106781068</v>
+        <v>-7.109053399517124</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.22799516469179</v>
       </c>
       <c r="E67">
-        <v>-8.169477869921112</v>
+        <v>-9.830612705414751</v>
       </c>
       <c r="F67">
-        <v>2.497141706817001</v>
+        <v>0.6956207982975895</v>
       </c>
       <c r="G67">
-        <v>-6.780220221646856</v>
+        <v>-7.796554391657572</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.41299712417815</v>
       </c>
       <c r="E68">
-        <v>-7.166642772448503</v>
+        <v>-10.04230527985132</v>
       </c>
       <c r="F68">
-        <v>2.398402394107098</v>
+        <v>0.3840559579943138</v>
       </c>
       <c r="G68">
-        <v>-6.91629026440198</v>
+        <v>-7.222681254061529</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.55915008082466</v>
       </c>
       <c r="E69">
-        <v>-8.735460136821775</v>
+        <v>-9.904272863623518</v>
       </c>
       <c r="F69">
-        <v>2.071983184169958</v>
+        <v>0.6027364463570659</v>
       </c>
       <c r="G69">
-        <v>-6.412054452224507</v>
+        <v>-7.786093067753474</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.6611126747468</v>
       </c>
       <c r="E70">
-        <v>-7.243522675676722</v>
+        <v>-9.65022547179321</v>
       </c>
       <c r="F70">
-        <v>2.008620694199141</v>
+        <v>0.3714417403778386</v>
       </c>
       <c r="G70">
-        <v>-7.051254584946988</v>
+        <v>-7.276278986342329</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.71825810680427</v>
       </c>
       <c r="E71">
-        <v>-6.660391077709011</v>
+        <v>-8.741084501539301</v>
       </c>
       <c r="F71">
-        <v>1.782595769653539</v>
+        <v>0.5010656939976842</v>
       </c>
       <c r="G71">
-        <v>-6.682529333328502</v>
+        <v>-7.054091722474143</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.72038652257766</v>
       </c>
       <c r="E72">
-        <v>-8.25137532234983</v>
+        <v>-9.91439400303066</v>
       </c>
       <c r="F72">
-        <v>1.528353956812552</v>
+        <v>0.2305227961690789</v>
       </c>
       <c r="G72">
-        <v>-6.682453190781099</v>
+        <v>-6.821562314341275</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.67601501941159</v>
       </c>
       <c r="E73">
-        <v>-7.259132325581162</v>
+        <v>-8.389013761338962</v>
       </c>
       <c r="F73">
-        <v>1.691816162874634</v>
+        <v>0.2087634687438986</v>
       </c>
       <c r="G73">
-        <v>-6.186589748272444</v>
+        <v>-6.335716582634453</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.58149966018476</v>
       </c>
       <c r="E74">
-        <v>-7.384240476991071</v>
+        <v>-10.13075543416914</v>
       </c>
       <c r="F74">
-        <v>1.409091399144469</v>
+        <v>0.5380190959755906</v>
       </c>
       <c r="G74">
-        <v>-6.502955411641816</v>
+        <v>-6.314721102824396</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.44090906985654</v>
       </c>
       <c r="E75">
-        <v>-7.63097438329899</v>
+        <v>-9.69501207972907</v>
       </c>
       <c r="F75">
-        <v>1.566362898783098</v>
+        <v>0.3296905013291085</v>
       </c>
       <c r="G75">
-        <v>-5.928926678405428</v>
+        <v>-5.677844973070483</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.26391042103486</v>
       </c>
       <c r="E76">
-        <v>-7.80706862356126</v>
+        <v>-10.90444068990561</v>
       </c>
       <c r="F76">
-        <v>0.9961559187527871</v>
+        <v>-0.09163466114961352</v>
       </c>
       <c r="G76">
-        <v>-6.016215832639391</v>
+        <v>-6.658127302158535</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.04976908270716</v>
       </c>
       <c r="E77">
-        <v>-8.54703486183662</v>
+        <v>-11.62994751067448</v>
       </c>
       <c r="F77">
-        <v>1.130723410387677</v>
+        <v>0.3020904664877875</v>
       </c>
       <c r="G77">
-        <v>-6.430891456342961</v>
+        <v>-6.293434295006882</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.81593901821886</v>
       </c>
       <c r="E78">
-        <v>-8.793818581358623</v>
+        <v>-11.76822446449869</v>
       </c>
       <c r="F78">
-        <v>1.497287981575292</v>
+        <v>-0.4914887306797652</v>
       </c>
       <c r="G78">
-        <v>-5.961449477783227</v>
+        <v>-6.106044175301975</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.564463664979</v>
       </c>
       <c r="E79">
-        <v>-8.42791335306485</v>
+        <v>-10.86483012776051</v>
       </c>
       <c r="F79">
-        <v>1.117822542000507</v>
+        <v>-0.03692474844780009</v>
       </c>
       <c r="G79">
-        <v>-5.60949876041223</v>
+        <v>-5.870551828911458</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.30427007881418</v>
       </c>
       <c r="E80">
-        <v>-10.01095465429622</v>
+        <v>-13.07601605859583</v>
       </c>
       <c r="F80">
-        <v>0.8762598787185283</v>
+        <v>0.0400449427484725</v>
       </c>
       <c r="G80">
-        <v>-5.434063020649631</v>
+        <v>-5.11555874486189</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.04448952918497</v>
       </c>
       <c r="E81">
-        <v>-11.74291935174383</v>
+        <v>-13.57080165714791</v>
       </c>
       <c r="F81">
-        <v>1.183175750307031</v>
+        <v>-0.5980175009347574</v>
       </c>
       <c r="G81">
-        <v>-5.148657579163523</v>
+        <v>-4.949253489696601</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.781538630222057</v>
       </c>
       <c r="E82">
-        <v>-11.81655233910855</v>
+        <v>-12.66279733386992</v>
       </c>
       <c r="F82">
-        <v>0.7856623981198992</v>
+        <v>-0.3065213819919304</v>
       </c>
       <c r="G82">
-        <v>-5.035546169723244</v>
+        <v>-5.238532269463657</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.527678689822146</v>
       </c>
       <c r="E83">
-        <v>-13.30095441950484</v>
+        <v>-15.729896551473</v>
       </c>
       <c r="F83">
-        <v>0.7846187359216247</v>
+        <v>-0.3486487511955774</v>
       </c>
       <c r="G83">
-        <v>-4.563584866008126</v>
+        <v>-5.144774309245958</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.277007346642684</v>
       </c>
       <c r="E84">
-        <v>-13.39862907537628</v>
+        <v>-14.28152753875574</v>
       </c>
       <c r="F84">
-        <v>0.6029439118319885</v>
+        <v>-0.5208134212629998</v>
       </c>
       <c r="G84">
-        <v>-3.810458929642706</v>
+        <v>-5.04215070807409</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.032619812773749</v>
       </c>
       <c r="E85">
-        <v>-13.56886347027262</v>
+        <v>-16.88219846204277</v>
       </c>
       <c r="F85">
-        <v>0.4916402682419463</v>
+        <v>-0.5198418176838776</v>
       </c>
       <c r="G85">
-        <v>-3.566868988863132</v>
+        <v>-4.851075951183975</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.796380587690221</v>
       </c>
       <c r="E86">
-        <v>-15.04297685772349</v>
+        <v>-15.52990102539824</v>
       </c>
       <c r="F86">
-        <v>0.6975640054558336</v>
+        <v>-0.7509844878952227</v>
       </c>
       <c r="G86">
-        <v>-3.768795714030978</v>
+        <v>-3.755397936233547</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.562398852254415</v>
       </c>
       <c r="E87">
-        <v>-16.54613134898554</v>
+        <v>-19.70031312175611</v>
       </c>
       <c r="F87">
-        <v>0.18520821881061</v>
+        <v>-0.449308307327951</v>
       </c>
       <c r="G87">
-        <v>-3.217176063549916</v>
+        <v>-4.202569874950603</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.33973589164067</v>
       </c>
       <c r="E88">
-        <v>-19.22934276801038</v>
+        <v>-19.90739118117886</v>
       </c>
       <c r="F88">
-        <v>0.2737167913067743</v>
+        <v>-0.631373514925743</v>
       </c>
       <c r="G88">
-        <v>-3.561780680369272</v>
+        <v>-4.272803098566241</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.122050416831039</v>
       </c>
       <c r="E89">
-        <v>-19.56926814092215</v>
+        <v>-22.2897987142442</v>
       </c>
       <c r="F89">
-        <v>0.2946866413331081</v>
+        <v>-0.3182352627954783</v>
       </c>
       <c r="G89">
-        <v>-2.933541763927318</v>
+        <v>-4.567219845010245</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.913749770664723</v>
       </c>
       <c r="E90">
-        <v>-19.97261026383733</v>
+        <v>-21.98506411284604</v>
       </c>
       <c r="F90">
-        <v>0.4028537553576224</v>
+        <v>-0.7389111058488701</v>
       </c>
       <c r="G90">
-        <v>-2.937090668745417</v>
+        <v>-3.542688764244295</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.715069215652058</v>
       </c>
       <c r="E91">
-        <v>-22.68082338785852</v>
+        <v>-26.06605696144845</v>
       </c>
       <c r="F91">
-        <v>0.2771170079072229</v>
+        <v>-0.8694013466044611</v>
       </c>
       <c r="G91">
-        <v>-3.141146074695014</v>
+        <v>-3.712602514047389</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.520931213388427</v>
       </c>
       <c r="E92">
-        <v>-24.95018209579637</v>
+        <v>-27.63868277246217</v>
       </c>
       <c r="F92">
-        <v>-0.218888598867004</v>
+        <v>-0.9900488550955959</v>
       </c>
       <c r="G92">
-        <v>-2.807727791252856</v>
+        <v>-3.262378252343125</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.336874718892474</v>
       </c>
       <c r="E93">
-        <v>-27.24356435834492</v>
+        <v>-27.92370039803093</v>
       </c>
       <c r="F93">
-        <v>-0.05411191689510669</v>
+        <v>-1.129323120711172</v>
       </c>
       <c r="G93">
-        <v>-2.721461595590527</v>
+        <v>-3.917604736021218</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.154166185025204</v>
       </c>
       <c r="E94">
-        <v>-28.00689752249986</v>
+        <v>-31.30598367080487</v>
       </c>
       <c r="F94">
-        <v>-0.6154921120057162</v>
+        <v>-1.30220441770533</v>
       </c>
       <c r="G94">
-        <v>-2.922497784008309</v>
+        <v>-2.883175124092846</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.974248194019272</v>
       </c>
       <c r="E95">
-        <v>-30.92757306153892</v>
+        <v>-32.82879626773422</v>
       </c>
       <c r="F95">
-        <v>-0.01707774591551293</v>
+        <v>-1.169149365219685</v>
       </c>
       <c r="G95">
-        <v>-2.643226783406471</v>
+        <v>-3.563856392422395</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.790224945823498</v>
       </c>
       <c r="E96">
-        <v>-33.35389320705663</v>
+        <v>-35.09736928543174</v>
       </c>
       <c r="F96">
-        <v>-0.09596055385763637</v>
+        <v>-1.155217504281564</v>
       </c>
       <c r="G96">
-        <v>-2.658157343788584</v>
+        <v>-3.494311762278925</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.595787506103227</v>
       </c>
       <c r="E97">
-        <v>-35.85863293696517</v>
+        <v>-37.5435535821841</v>
       </c>
       <c r="F97">
-        <v>-0.6512735716061974</v>
+        <v>-1.069938899999939</v>
       </c>
       <c r="G97">
-        <v>-3.333508633799906</v>
+        <v>-4.483833823967083</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.389059502603857</v>
       </c>
       <c r="E98">
-        <v>-38.79589401205732</v>
+        <v>-39.30616019900462</v>
       </c>
       <c r="F98">
-        <v>-0.3345775241368979</v>
+        <v>-0.8190775074354572</v>
       </c>
       <c r="G98">
-        <v>-2.659421972184585</v>
+        <v>-3.539265660156689</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.167878388162134</v>
       </c>
       <c r="E99">
-        <v>-40.21114629435649</v>
+        <v>-43.67283635885492</v>
       </c>
       <c r="F99">
-        <v>-0.6340864031588908</v>
+        <v>-1.253757270046122</v>
       </c>
       <c r="G99">
-        <v>-3.411644129617784</v>
+        <v>-4.03419883936881</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.932089737769774</v>
       </c>
       <c r="E100">
-        <v>-43.33851044405364</v>
+        <v>-45.02286729425861</v>
       </c>
       <c r="F100">
-        <v>-0.6285252198368252</v>
+        <v>-1.280783211493097</v>
       </c>
       <c r="G100">
-        <v>-3.122610330220635</v>
+        <v>-4.202225578214519</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.699024146672793</v>
       </c>
       <c r="E101">
-        <v>-46.06012332266352</v>
+        <v>-46.5885645400406</v>
       </c>
       <c r="F101">
-        <v>-0.6009410220546586</v>
+        <v>-1.567160792917223</v>
       </c>
       <c r="G101">
-        <v>-3.648060118213758</v>
+        <v>-3.957870901415373</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.454993565634305</v>
       </c>
       <c r="E102">
-        <v>-47.73551832280732</v>
+        <v>-49.74021942431489</v>
       </c>
       <c r="F102">
-        <v>-0.5619177164452729</v>
+        <v>-1.899884736103728</v>
       </c>
       <c r="G102">
-        <v>-4.046421373499799</v>
+        <v>-4.245252738588427</v>
       </c>
     </row>
   </sheetData>
